--- a/Project_CNN/Main/Results/Experimento 17 - ResNet/training_metrics.xlsx
+++ b/Project_CNN/Main/Results/Experimento 17 - ResNet/training_metrics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marci_wawp\Desktop\Arquivos\Mestrado\Projeto-Classificadores\Project_CNN\Main\Results\Experimento 17 - ResNet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1272EA9D-6AA5-432A-861A-99D4C911C8B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADAF7987-1D80-43E7-816D-B735657C1B41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6548,7 +6548,7085 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR" sz="1600" b="0" baseline="0"/>
+              <a:t>Accuracy curve: ResNet-10, Batch size = 32</a:t>
+            </a:r>
+            <a:endParaRPr lang="pt-BR" sz="1600" b="0"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Worksheet!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>accuracy</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Worksheet!$B$2:$B$504</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="503"/>
+                <c:pt idx="0">
+                  <c:v>0.44517701864242998</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.45607680082321</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.45408439636230002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.46558594703674</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.46766889095306002</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.49429452419281</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.50688278675079002</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.50987142324447998</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.51304113864899004</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.51883715391159002</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.51430898904800004</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.53559136390686002</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.54247421026230003</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.55451911687850997</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.57480525970458995</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.58413332700729004</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.59282737970351995</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.60460060834884999</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.61030608415604004</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.62180763483046997</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.62624526023865001</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.63656944036483998</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.64227497577667003</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.63656944036483998</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.64852380752562999</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.65785181522368996</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.66500633955001998</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.67279475927353005</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.68194168806076005</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.67813801765441994</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.71988767385482999</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.72604602575302002</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.73093640804291005</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.73772865533829002</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.73292881250381003</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.7343778014183</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.74189460277556996</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.73845314979553001</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.74479258060455</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.74723780155181996</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.74886792898178001</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.74805289506911998</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.75403004884720004</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.75022643804550004</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.75312441587447998</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.75882995128632003</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.75520741939545</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.75756204128265003</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.76127511262893999</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.76643723249435003</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.76652783155440996</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.76580327749251997</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.76199966669082997</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.77005976438521995</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.76734286546706998</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.76969754695892001</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.77821046113967995</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.77241444587707997</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.77467852830886996</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.78011232614517001</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.77911609411240001</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.78572720289230003</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.78590834140777999</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.78554612398148005</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.78599894046783003</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.78672343492508001</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.79061764478683005</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.79215723276137995</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.78645175695419001</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.78771960735321001</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.79097992181777999</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.79677593708037997</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.78934973478317005</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.79251945018768</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.78953087329865002</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.78944033384322998</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.78971201181411999</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.78871583938598999</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.79215723276137995</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.79369682073592995</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>0.79297226667403997</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>0.79143273830413996</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>0.79577976465224998</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>0.79116100072860995</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>0.79731935262679998</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>0.79858720302581998</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>0.79813438653946001</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>0.79813438653946001</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>0.79043650627135997</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>0.79958343505858998</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>0.79251945018768</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>0.79360622167587003</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>0.79360622167587003</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0.79641371965408003</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>0.79641371965408003</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>0.79424017667769997</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0.79768157005310003</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>0.79831552505492998</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>0.79306286573410001</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>0.79324400424956998</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>0.79931169748305997</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>0.79496467113494995</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>0.79904001951217996</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>0.80048906803131004</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>0.79577976465224998</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>0.79967397451401001</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>0.79387789964676003</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>0.79867780208588002</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>0.79904001951217996</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>0.80356818437576005</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>0.80057960748671997</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>0.79396849870681996</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>0.79913061857223999</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>0.80030792951583996</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>0.79559862613678001</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>0.79822498559952004</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>0.80148524045944003</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>0.79442131519318004</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>0.80465495586394997</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>0.79405903816223</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>0.80393046140670998</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>0.79894948005676003</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>0.80619454383849998</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>0.80067014694214</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>0.80211919546126997</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>0.80438327789306996</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>0.80501723289490001</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>0.80483609437943004</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>0.80365878343581998</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>0.79759103059768999</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>0.80139470100402999</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>0.80338704586028997</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>0.80130410194396995</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>0.80537945032119995</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>0.80411159992217995</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>0.80637568235396995</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>0.80057960748671997</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>0.80528891086578003</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>0.80393046140670998</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>0.80320596694946</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>0.80827748775482</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>0.81108492612839</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>0.80900198221206998</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>0.79840606451035001</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>0.80592286586760997</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>0.80845862627028997</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>0.80836802721024004</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>0.80374932289124001</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>0.80664736032485995</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>0.80248141288757002</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>0.81036043167114002</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>0.81036043167114002</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>0.80447381734848</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>0.80474549531937001</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>0.81090384721756004</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>0.80719071626662997</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>0.80836802721024004</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>0.80710017681122004</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>0.80764353275298995</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>0.80329650640488004</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>0.80990761518478005</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>0.81171888113021995</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>0.80691903829574996</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>0.80900198221206998</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>0.81008875370026001</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>0.80574172735214</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>0.81090384721756004</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>0.80764353275298995</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>0.80954539775848</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>0.80936425924301003</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>0.80936425924301003</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>0.81362074613571</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>0.81389242410660001</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>0.80537945032119995</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>0.81226229667663996</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>0.80963593721390004</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>0.81217169761658004</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>0.81262451410294001</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>0.81434524059295998</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>0.81026989221572998</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>0.81099438667296997</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>0.81461691856384</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>0.81343960762024003</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>0.81706213951110995</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>0.81244337558746005</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>0.81217169761658004</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>0.80927366018294999</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>0.81787717342376998</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>0.80863976478577004</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>0.81126606464385997</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>0.81271511316299005</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>0.81108492612839</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>0.81878280639648005</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>0.80945479869842996</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>0.81697154045105003</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>0.81253397464751997</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>0.81706213951110995</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>0.81434524059295998</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>0.81452637910842995</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>0.81688100099563998</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>0.81525087356567005</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>0.81434524059295998</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>0.81787717342376998</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>0.81679046154021995</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>0.8158848285675</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>0.81371128559113004</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>0.81506973505019997</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>0.81624704599380005</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>0.81642818450928001</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>0.81914508342742998</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>0.81579422950744995</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>0.82159030437469005</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>0.82213366031646995</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>0.81733381748198997</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>0.81579422950744995</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>0.82032239437103005</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>0.81842058897018</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>0.81534141302108998</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>0.81896394491196001</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>0.82140916585921997</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>0.82258647680283004</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>0.81869226694107</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>0.81679046154021995</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>0.81832998991012995</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>0.81878280639648005</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>0.81814891099929998</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>0.81923562288284002</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>0.81860172748565996</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>0.81950736045837003</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>0.82294875383376997</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>0.82530337572098</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>0.81950736045837003</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>0.82312989234924006</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>0.82539397478104004</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>0.82258647680283004</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>0.82512223720551003</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>0.81307733058928999</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>0.82394492626189997</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>0.82023185491562001</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>0.82620900869369995</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>0.82240533828734996</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>0.82430720329285001</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>0.81932622194289995</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>0.82566565275192005</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>0.82602787017821999</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>0.82412606477737005</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>0.82322043180465998</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>0.82349210977553999</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>0.82992213964462003</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>0.82521283626555997</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>0.82702410221099998</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>0.82856369018554998</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>0.82457888126373002</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>0.82494115829467995</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>0.82485055923462003</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>0.82276761531830001</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>0.82521283626555997</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>0.82702410221099998</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>0.82620900869369995</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>0.83082777261733998</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>0.82204312086105003</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>0.82149970531464001</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>0.82729578018187999</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>0.82629960775375</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>0.82566565275192005</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>0.82765805721283003</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>0.83019381761551003</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>0.82494115829467995</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>0.83010321855545</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>0.82756745815277</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>0.82602787017821999</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>0.82838255167007002</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>0.83372575044632002</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>0.83109945058822998</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>0.82802027463912997</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>0.82720524072646995</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>0.83137112855911</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>0.83082777261733998</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>0.83191448450089001</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>0.83490312099456998</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>0.82738631963730003</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>0.82892590761185003</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>0.82693350315094005</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>0.82892590761185003</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>0.82485055923462003</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>0.82729578018187999</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>0.82639014720917003</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>0.82892590761185003</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>0.82711464166641002</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>0.83055603504180997</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>0.83336353302001998</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>0.83291071653366</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>0.83118999004364003</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>0.83771055936812999</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>0.83282011747359996</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>0.82919758558273005</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>0.83073717355728005</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>0.83191448450089001</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>0.83091831207275002</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>0.82928818464278997</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>0.83481252193451005</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>0.83445030450821001</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>0.83508419990539995</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>0.82765805721283003</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>0.83236730098723999</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>0.83118999004364003</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>0.83408802747725996</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>0.82910704612732</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>0.84024631977080999</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>0.83626157045364002</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>0.83227676153182995</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>0.83698606491089</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>0.83925014734268</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>0.83426916599274004</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>0.83553701639175004</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>0.83218622207642001</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>0.82992213964462003</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>0.83390688896178999</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>0.83245790004730003</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>0.83635210990905995</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>0.83019381761551003</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>0.83472198247910001</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>0.83716720342635997</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>0.82792973518372004</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>0.83644264936446999</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>0.83635210990905995</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>0.83191448450089001</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>0.83707660436630005</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>0.83635210990905995</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>0.83725774288177002</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>0.83843505382537997</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>0.84015578031539995</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>0.83771055936812999</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>0.83445030450821001</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>0.84078973531723</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>0.84015578031539995</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>0.84441226720810003</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>0.83861619234085005</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>0.83752942085266002</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>0.84404999017714999</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>0.83608043193817005</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>0.83707660436630005</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>0.83789169788360995</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>0.83725774288177002</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>0.83906900882721003</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>0.83897846937179998</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>0.83598983287811002</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>0.84013730287552002</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>0.84187644720078003</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>0.83716720342635997</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>0.83807283639908003</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>0.83870673179625999</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>0.83780109882355003</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>0.83870673179625999</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>0.83580875396729004</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>0.84115195274353005</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>0.83499366044998002</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>0.83952182531357</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>0.84296321868895996</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>0.83906900882721003</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>0.84232926368713001</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>0.83752942085266002</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>0.83852565288544001</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>0.84078973531723</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>0.83771055936812999</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>0.83915954828261996</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>0.84232926368713001</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>0.84024631977080999</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>0.83879733085632002</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>0.84649521112442005</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>0.83906900882721003</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>0.84604239463805997</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>0.84386885166168002</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>0.84504616260528997</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>0.84495562314987005</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>0.83617097139358998</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>0.84423112869262995</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>0.83789169788360995</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>0.84395945072173995</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>0.84631407260894997</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>0.8405179977417</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>0.84513676166534002</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>0.84223872423171997</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>0.84450280666350996</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>0.84495562314987005</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>0.84513676166534002</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>0.84803479909896995</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>0.84450280666350996</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>0.83780109882355003</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>0.84459334611893</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>0.84441226720810003</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>0.84404999017714999</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>0.85138559341430997</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>0.84187644720078003</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>0.84495562314987005</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>0.84731024503707997</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>0.84604239463805997</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>0.84794420003891002</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>0.84604239463805997</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>0.84432166814803999</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>0.84604239463805997</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>0.84604239463805997</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>0.84884983301162997</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>0.84939324855803999</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>0.84703856706618996</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>0.84341603517532004</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>0.84631407260894997</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>0.84522730112076006</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>0.84767252206802002</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>0.84495562314987005</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>0.84740084409714</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>0.84522730112076006</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>0.84948378801346003</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>0.84894043207169001</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>0.85220068693161</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>0.84767252206802002</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>0.85138559341430997</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>0.84640461206436002</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>0.8524723649025</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>0.84767252206802002</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>0.84830647706984996</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>0.85319685935973999</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>0.85047996044159002</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>0.84459334611893</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>0.84957432746886996</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>0.84595179557800004</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>0.85093277692795</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>0.85174787044525002</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>0.84921211004257002</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>0.85138559341430997</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>0.85238182544707997</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>0.84794420003891002</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>0.85229122638702004</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>0.84812533855437999</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>0.85102337598801003</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>0.85029888153076005</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>0.85057055950164995</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>0.84577071666717996</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>0.85455530881882003</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>0.85301578044891002</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>0.85038942098617998</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>0.84649521112442005</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>0.85111391544341997</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>0.85220068693161</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>0.85102337598801003</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>0.85582321882248003</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>0.85301578044891002</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>0.85428363084793002</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>0.85066109895705999</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>0.84984606504439997</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>0.85165733098983998</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>0.85020828247070002</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>0.85455530881882003</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>0.85482704639435003</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>0.85591375827788996</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>0.84794420003891002</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>0.85355913639069003</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>0.85310631990432995</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>0.85292518138884998</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>0.85201954841614003</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>0.85872125625609996</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>0.85473644733428999</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>0.85274404287338001</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>0.85428363084793002</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>0.85102337598801003</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>0.85926461219787997</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>0.85301578044891002</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>0.85700052976607999</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>0.85473644733428999</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>0.85709112882614003</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>0.85518926382064997</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>0.85319685935973999</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>0.85718166828155995</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>0.85256296396255005</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>0.85555154085159002</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>0.85790616273880005</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>0.85573267936706998</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>0.8524723649025</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>0.85437422990798995</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>0.85446476936339999</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>0.86125701665877996</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>0.86143815517426003</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>0.85700052976607999</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>0.85763448476791004</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>0.85518926382064997</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>0.85428363084793002</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>0.85645717382430997</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>0.85917407274246005</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>0.86017024517059004</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>0.85546094179152998</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>0.85654771327972001</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>0.85129505395889005</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>0.85872125625609996</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>0.85283464193344005</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>0.86216264963150002</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>0.85863065719604004</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>0.85473644733428999</c:v>
+                </c:pt>
+                <c:pt idx="497">
+                  <c:v>0.85763448476791004</c:v>
+                </c:pt>
+                <c:pt idx="498">
+                  <c:v>0.85582321882248003</c:v>
+                </c:pt>
+                <c:pt idx="499">
+                  <c:v>0.85654771327972001</c:v>
+                </c:pt>
+                <c:pt idx="501">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="502">
+                  <c:v>0.85669866005579398</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-BFEE-40B5-A9E2-B26E9469C8C8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Worksheet!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>val_accuracy</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Worksheet!$E$2:$E$504</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="503"/>
+                <c:pt idx="0">
+                  <c:v>0.45530521869659002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.45530521869659002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.45784884691237998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.45530521869659002</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.51380813121795998</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.50872093439101995</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.52252906560898005</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.55995637178420998</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.54215115308761996</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.54433137178420998</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.54396802186965998</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.50799417495728005</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.55050873756409002</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.61882269382476995</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.61518895626068004</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.61191862821579002</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.62281978130340998</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.63771802186965998</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.67005813121795998</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.68277615308761996</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.67369186878204002</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.68786334991455</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.70784884691238004</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.67732560634613004</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.65915697813034002</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.68931686878204002</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.72165697813034002</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.71366280317306996</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.72383719682693004</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.73292154073714999</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.74164241552353005</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.75654071569443004</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.76526165008545</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.76962208747864003</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.76816862821579002</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.76598834991455</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.765625</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.77289241552353005</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.77834302186965998</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.78125</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.78924417495728005</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.78125</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.77579939365386996</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.78197675943375</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.77906978130340998</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.78161334991455</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.79142439365386996</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.78997093439101995</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.79651165008545</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.79251456260680997</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.77906978130340998</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.79651165008545</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.80123543739319003</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.80523258447646995</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.77398258447646995</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.80450582504271995</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.80123543739319003</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.80341571569443004</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.79796510934830001</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.8125</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.81795060634613004</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.81795060634613004</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.81976741552353005</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.81540697813034002</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.81577032804489003</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.82485467195510997</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.82231104373931996</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.82412791252135997</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.82303780317306996</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.82267439365386996</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.82485467195510997</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.82376456260680997</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.82703489065169999</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.82085758447646995</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.82594478130340998</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.82703489065169999</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.82885175943375</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.82594478130340998</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.82376456260680997</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.82703489065169999</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>0.82412791252135997</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>0.828125</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>0.82994186878204002</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>0.82848834991455</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>0.82485467195510997</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>0.82957845926285001</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>0.82885175943375</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>0.82739824056625</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>0.82739824056625</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>0.83066862821579002</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>0.82885175943375</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>0.82594478130340998</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>0.82885175943375</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0.83575582504271995</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>0.82921510934830001</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>0.82485467195510997</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0.82848834991455</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>0.82957845926285001</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>0.83175873756409002</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>0.82194769382476995</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>0.82231104373931996</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>0.83430230617523005</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>0.82957845926285001</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>0.82885175943375</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>0.83284884691238004</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>0.82630813121795998</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>0.83212208747864003</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>0.83030521869659002</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>0.83212208747864003</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>0.83103197813034002</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>0.82921510934830001</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>0.82739824056625</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>0.83175873756409002</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>0.82994186878204002</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>0.83248543739319003</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>0.82776165008545</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>0.83430230617523005</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>0.82994186878204002</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>0.83103197813034002</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>0.82885175943375</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>0.83393895626068004</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>0.82994186878204002</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>0.83575582504271995</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>0.83284884691238004</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>0.83575582504271995</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>0.83648258447646995</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>0.83502906560898005</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>0.83284884691238004</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>0.82885175943375</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>0.83430230617523005</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>0.83357560634613004</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>0.83175873756409002</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>0.83829939365386996</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>0.83611917495728005</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>0.83321219682693004</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>0.83611917495728005</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>0.83648258447646995</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>0.83648258447646995</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>0.83393895626068004</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>0.83321219682693004</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>0.83757269382476995</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>0.83793604373931996</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>0.83466571569443004</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>0.83793604373931996</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>0.83575582504271995</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>0.83321219682693004</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>0.83430230617523005</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>0.83611917495728005</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>0.83648258447646995</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>0.83684593439101995</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>0.83866280317306996</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>0.84047967195510997</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>0.83502906560898005</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>0.83648258447646995</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>0.83430230617523005</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>0.83720928430556996</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>0.83321219682693004</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>0.83975291252135997</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>0.84120637178420998</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>0.83975291252135997</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>0.84011626243590998</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>0.84047967195510997</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>0.83757269382476995</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>0.84011626243590998</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>0.83975291252135997</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>0.83902615308761996</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>0.83539241552353005</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>0.84120637178420998</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>0.84120637178420998</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>0.84156978130340998</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>0.84265989065169999</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>0.83938956260680997</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>0.83430230617523005</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>0.83284884691238004</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>0.83866280317306996</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>0.83321219682693004</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>0.83684593439101995</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>0.83975291252135997</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>0.83611917495728005</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>0.84265989065169999</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>0.83684593439101995</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>0.84411334991455</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>0.84338665008545</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>0.83720928430556996</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>0.83757269382476995</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>0.84084302186965998</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>0.83466571569443004</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>0.84556686878204002</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>0.84120637178420998</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>0.83902615308761996</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>0.83975291252135997</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>0.83575582504271995</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>0.83502906560898005</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>0.84193313121795998</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>0.83902615308761996</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>0.83866280317306996</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>0.84593021869659002</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>0.84156978130340998</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>0.84520345926285001</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>0.84047967195510997</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>0.84447675943375</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>0.84193313121795998</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>0.83611917495728005</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>0.84047967195510997</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>0.84193313121795998</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>0.84520345926285001</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>0.82957845926285001</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>0.84702032804489003</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>0.84738373756409002</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>0.84375</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>0.84375</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>0.84665697813034002</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>0.84338665008545</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>0.84629362821579002</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>0.83938956260680997</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>0.84702032804489003</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>0.84520345926285001</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>0.84593021869659002</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>0.84338665008545</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>0.84338665008545</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>0.84338665008545</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>0.84084302186965998</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>0.84629362821579002</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>0.83938956260680997</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>0.84447675943375</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>0.84302324056625</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>0.84338665008545</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>0.84702032804489003</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>0.84883719682693004</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>0.84156978130340998</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>0.84375</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>0.85029071569443004</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>0.84992730617523005</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>0.84447675943375</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>0.84156978130340998</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>0.84084302186965998</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>0.84302324056625</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>0.84120637178420998</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>0.84375</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>0.83975291252135997</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>0.85065406560898005</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>0.84302324056625</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>0.84447675943375</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>0.85319769382476995</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>0.84956395626068004</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>0.85029071569443004</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>0.84265989065169999</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>0.84738373756409002</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>0.84847384691238004</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>0.84593021869659002</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>0.85428780317306996</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>0.85210758447646995</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>0.84593021869659002</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>0.84920060634613004</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>0.83684593439101995</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>0.84847384691238004</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>0.84738373756409002</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>0.85319769382476995</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>0.84447675943375</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>0.84156978130340998</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>0.84629362821579002</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>0.84811043739319003</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>0.85247093439101995</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>0.84411334991455</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>0.85138082504271995</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>0.84992730617523005</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>0.85029071569443004</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>0.84665697813034002</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>0.84556686878204002</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>0.85065406560898005</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>0.84920060634613004</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>0.84629362821579002</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>0.84484010934830001</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>0.84556686878204002</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>0.85247093439101995</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>0.84883719682693004</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>0.85029071569443004</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>0.85792154073714999</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>0.85428780317306996</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>0.84593021869659002</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>0.85174417495728005</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>0.85719478130340998</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>0.84447675943375</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>0.85174417495728005</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>0.85574126243590998</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>0.85356104373931996</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>0.85465115308761996</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>0.84302324056625</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>0.84738373756409002</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>0.85610467195510997</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>0.85101741552353005</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>0.85138082504271995</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>0.84702032804489003</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>0.85828489065169999</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>0.85646802186965998</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>0.85683137178420998</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>0.85683137178420998</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>0.84920060634613004</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>0.85755813121795998</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>0.85683137178420998</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>0.85356104373931996</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>0.84629362821579002</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>0.85864824056625</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>0.85574126243590998</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>0.85210758447646995</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>0.84338665008545</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>0.84774708747864003</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>0.85138082504271995</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>0.85610467195510997</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>0.85501456260680997</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>0.85283428430556996</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>0.85392439365386996</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>0.85537791252135997</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>0.84447675943375</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>0.84811043739319003</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>0.85610467195510997</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>0.85319769382476995</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>0.85247093439101995</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>0.84992730617523005</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>0.84047967195510997</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>0.85174417495728005</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>0.85210758447646995</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>0.85428780317306996</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>0.85465115308761996</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>0.85864824056625</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>0.85901165008545</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>0.85719478130340998</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>0.85465115308761996</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>0.85319769382476995</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>0.84520345926285001</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>0.85646802186965998</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>0.85719478130340998</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>0.85319769382476995</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>0.84629362821579002</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>0.85428780317306996</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>0.83357560634613004</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>0.83321219682693004</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>0.85465115308761996</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>0.85428780317306996</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>0.85610467195510997</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>0.85719478130340998</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>0.84193313121795998</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>0.85537791252135997</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>0.85719478130340998</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>0.85247093439101995</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>0.85428780317306996</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>0.84738373756409002</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>0.86191862821579002</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>0.85755813121795998</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>0.85101741552353005</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>0.86228197813034002</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>0.85610467195510997</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>0.86191862821579002</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>0.85029071569443004</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>0.83975291252135997</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>0.85610467195510997</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>0.86046510934830001</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>0.85501456260680997</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>0.86082845926285001</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>0.85901165008545</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>0.86264532804489003</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>0.85901165008545</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>0.85319769382476995</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>0.86010175943375</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>0.86119186878204002</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>0.86446219682693004</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>0.85973834991455</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>0.86446219682693004</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>0.86082845926285001</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>0.86155521869659002</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>0.86046510934830001</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>0.85792154073714999</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>0.86373543739319003</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>0.86264532804489003</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>0.85792154073714999</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>0.85501456260680997</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>0.86010175943375</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>0.84956395626068004</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>0.86264532804489003</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>0.85319769382476995</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>0.84665697813034002</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>0.859375</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>0.86010175943375</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>0.86119186878204002</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>0.86446219682693004</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>0.86191862821579002</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>0.85465115308761996</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>0.85610467195510997</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>0.86119186878204002</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>0.86482560634613004</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>0.86337208747864003</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>0.85537791252135997</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>0.85828489065169999</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>0.86300873756409002</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>0.85792154073714999</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>0.86446219682693004</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>0.85319769382476995</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>0.86300873756409002</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>0.86082845926285001</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>0.86010175943375</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>0.86409884691238004</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>0.85792154073714999</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>0.85792154073714999</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>0.85283428430556996</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>0.86555230617523005</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>0.86736917495728005</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>0.86191862821579002</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>0.86700582504271995</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>0.86119186878204002</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>0.86918604373931996</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>0.86191862821579002</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>0.85828489065169999</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>0.85828489065169999</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>0.85683137178420998</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>0.86882269382476995</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>0.86954939365386996</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>0.87027615308761996</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>0.86882269382476995</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>0.86954939365386996</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>0.86882269382476995</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>0.87063956260680997</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>0.86155521869659002</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>0.86191862821579002</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>0.86918604373931996</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>0.87136626243590998</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>0.86991280317306996</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>0.87063956260680997</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>0.87281978130340998</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>0.85610467195510997</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>0.86845928430556996</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>0.87136626243590998</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>0.86446219682693004</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>0.87063956260680997</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>0.86809593439101995</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>0.86882269382476995</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>0.87354654073714999</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>0.86845928430556996</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>0.86627906560898005</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>0.86954939365386996</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>0.87172967195510997</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>0.86991280317306996</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>0.87100291252135997</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>0.86845928430556996</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>0.87209302186965998</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>0.86991280317306996</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>0.87136626243590998</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>0.86918604373931996</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>0.87318313121795998</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>0.85138082504271995</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>0.87390989065169999</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>0.86918604373931996</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>0.86773258447646995</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>0.86591571569443004</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>0.86882269382476995</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>0.85755813121795998</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>0.86373543739319003</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>0.87572675943375</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>0.86191862821579002</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>0.86446219682693004</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>0.87027615308761996</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>0.86954939365386996</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>0.86918604373931996</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>0.86736917495728005</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>0.86991280317306996</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>0.87245637178420998</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>0.86010175943375</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>0.86591571569443004</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>0.87281978130340998</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>0.87536334991455</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>0.86482560634613004</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>0.875</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>0.87100291252135997</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>0.87390989065169999</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>0.87790697813034002</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>0.87681686878204002</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>0.87463665008545</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>0.86409884691238004</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>0.875</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>0.85210758447646995</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>0.87463665008545</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>0.86882269382476995</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>0.86700582504271995</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>0.86373543739319003</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>0.87572675943375</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>0.86918604373931996</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>0.87536334991455</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>0.87318313121795998</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>0.86918604373931996</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>0.86991280317306996</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>0.87354654073714999</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>0.87427324056625</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>0.87245637178420998</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>0.86228197813034002</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>0.87172967195510997</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>0.86918604373931996</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>0.84956395626068004</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>0.86409884691238004</c:v>
+                </c:pt>
+                <c:pt idx="497">
+                  <c:v>0.86228197813034002</c:v>
+                </c:pt>
+                <c:pt idx="498">
+                  <c:v>0.87536334991455</c:v>
+                </c:pt>
+                <c:pt idx="499">
+                  <c:v>0.88117730617523005</c:v>
+                </c:pt>
+                <c:pt idx="501">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="502">
+                  <c:v>0.86957364082336419</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-BFEE-40B5-A9E2-B26E9469C8C8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="393590320"/>
+        <c:axId val="393592720"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="393590320"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="499"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="pt-BR" sz="1800" b="0"/>
+                  <a:t>Epochs</a:t>
+                </a:r>
+                <a:endParaRPr lang="pt-BR" sz="1400" b="0"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="393592720"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="50"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="393592720"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="pt-BR" sz="1800" b="0"/>
+                  <a:t>Accuracy</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="pt-BR" sz="1600" b="1" baseline="0"/>
+                  <a:t> (%)</a:t>
+                </a:r>
+                <a:endParaRPr lang="pt-BR" sz="1600" b="1"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="393590320"/>
+        <c:crossesAt val="1"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR" sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Loss curve: ResNet-10, Batch size = 32</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Worksheet!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>loss</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Worksheet!$C$2:$C$504</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="503"/>
+                <c:pt idx="0">
+                  <c:v>1.2496991157532</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.2423892021178999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.2372460365294999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.2334513664246001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.2249506711960001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.2131553888321001</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.1945708990096999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.188359618187</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.1839367151260001</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.1641004085541</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.1632971763611</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.1400567293167001</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.1256251335144001</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.1073095798492001</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.0774390697478999</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.0562326908112001</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.0345503091812001</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.0004756450653001</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.99949675798416004</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.98766320943831998</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.97249668836594005</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.94385063648223999</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.94099658727645996</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.95070463418961004</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.92588275671005005</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.90022593736649004</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.88877165317535001</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.87209868431090998</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.85371911525725996</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.85756093263625999</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.79402697086333995</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.76920527219771995</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.76192033290863004</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.75364047288894997</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.74807298183440996</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.75091809034348</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.74151766300201005</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.73752492666244995</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.73488491773605003</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.73165428638457997</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.72345060110091997</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.72128528356552002</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.71635335683822998</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.71865755319595004</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.71702021360396995</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.70925331115723</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.71123707294464</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.70685249567032005</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.70439034700393999</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.69376605749130005</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.69531828165053999</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.69028699398041005</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.69375729560851995</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.67844229936599998</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.68922001123428001</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.67944234609604004</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.66806590557098</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.67346245050429998</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.67768162488937</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.668301820755</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.65846395492554</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.64517939090729004</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.64869493246078003</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.64895421266555997</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.64509248733520996</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.64156383275985995</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.64140480756759999</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.63973248004912997</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.64149659872054998</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.63241255283356002</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.63865619897841996</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.63415938615798995</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.64186877012252996</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.64104270935059005</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.64079862833023005</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.64097303152083995</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.63630211353302002</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.63740241527556996</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.63624727725982999</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.63861942291259999</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>0.63707154989242998</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>0.63652658462524003</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>0.63279402256011996</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>0.63670188188553001</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>0.63187700510025002</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>0.62620025873184004</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>0.62929832935332997</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>0.62828505039214999</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>0.63236731290817005</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>0.62303483486176003</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>0.6333202123642</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>0.63193643093108998</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>0.63077533245087003</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0.63172483444214</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>0.62915921211242998</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>0.63549530506134</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0.62062656879425004</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>0.62095755338669001</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>0.62482672929764005</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>0.62992209196090998</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>0.62525606155395996</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>0.63242828845978005</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>0.62030118703841997</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>0.61983096599579002</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>0.62805640697479004</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>0.62630611658096003</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>0.63014590740204002</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>0.62297040224074995</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>0.62047523260116999</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>0.61959564685821999</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>0.61801767349242998</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>0.62647539377213002</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>0.61742770671844005</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>0.62067133188248003</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>0.61689102649688998</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>0.61622750759125</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>0.61952859163284002</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>0.62503910064696999</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>0.61397451162338001</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>0.62253111600875999</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>0.61962062120438</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>0.61594671010971003</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>0.61143755912780995</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>0.61519074440001997</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>0.61521852016448997</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>0.61742085218429998</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>0.61550778150558005</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>0.61267161369323997</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>0.61719000339508001</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>0.61553955078125</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>0.61764734983444003</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>0.6113612651825</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>0.61497223377228005</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>0.61015444993973</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>0.61123257875443004</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>0.61530691385268999</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>0.61441177129744995</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>0.60860848426819003</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>0.61124956607819003</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>0.60709440708160001</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>0.60859876871108998</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>0.60540950298309004</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>0.60839366912841997</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>0.61960709095000999</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>0.60885196924210006</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>0.60517638921738004</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>0.60436111688614003</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>0.60377478599547996</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>0.61217671632767001</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>0.60540336370467995</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>0.60390836000443004</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>0.60185497999190996</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>0.61040842533112005</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>0.60981470346451006</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>0.59647679328918002</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>0.60699522495269997</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>0.60998362302779996</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>0.60418421030045</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>0.60345757007598999</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>0.60756021738052002</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>0.60018169879912997</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>0.59485906362534002</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>0.60097920894623003</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>0.60373818874358998</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>0.59762376546859997</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>0.60015052556991999</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>0.59750080108643</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>0.60345786809920998</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>0.60337996482848999</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>0.5998757481575</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>0.6006885766983</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>0.59200459718704002</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>0.59248918294907005</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>0.60515022277831998</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>0.59645169973373002</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>0.59773534536362005</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>0.59224200248717995</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>0.59511113166809004</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>0.59122306108474998</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>0.60204488039017001</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>0.59979999065399003</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>0.58668780326842995</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>0.59599560499190996</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>0.58901184797286998</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>0.59370499849319003</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>0.59338724613189997</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>0.59698247909545998</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>0.58974993228911998</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>0.59758436679839999</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>0.59342235326767001</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>0.59133744239806996</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>0.58881217241286998</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>0.58279937505722001</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>0.59167140722275002</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>0.58546876907348999</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>0.59112161397934004</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>0.58198952674866</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>0.59045207500457997</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>0.58922547101973999</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>0.58488255739212003</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>0.59166872501373002</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>0.59366273880005005</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>0.58185958862304998</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>0.58579295873642001</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>0.59123021364212003</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>0.58754700422286998</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>0.58840495347976995</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>0.58606910705565995</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>0.58300834894179998</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>0.58650362491607999</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>0.58655250072479004</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>0.57561981678009</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>0.57755446434020996</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>0.58255481719971003</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>0.58391219377518</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>0.57731401920319003</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>0.58442240953445002</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>0.58497250080108998</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>0.58100134134293002</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>0.57693976163864003</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>0.57564049959182995</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>0.57987624406814997</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>0.57973921298981002</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>0.58270221948624001</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>0.57597833871840998</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>0.58246785402297996</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>0.57685959339142001</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>0.57973796129226995</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>0.58003211021422996</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>0.58006507158278997</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>0.56826663017273005</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>0.58029323816299005</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>0.56999784708023005</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>0.57139760255813998</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>0.57891142368316995</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>0.57314270734786998</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>0.58669531345366999</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>0.57734072208404996</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>0.57545834779739002</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>0.57215672731400002</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>0.57457619905472002</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>0.57155323028563998</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>0.57179188728332997</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>0.57195484638214</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>0.56901866197586004</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>0.56547927856445002</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>0.57324415445328003</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>0.56827855110168002</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>0.56885057687759</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>0.57005679607391002</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>0.56499820947646995</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>0.56524145603179998</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>0.57251954078674006</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>0.56933605670928999</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>0.57441520690918002</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>0.56464493274688998</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>0.56511950492858998</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>0.57126402854919001</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>0.56527900695801003</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>0.56188917160034002</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>0.56682735681534002</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>0.56836915016174006</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>0.56643903255463002</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>0.56945627927779996</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>0.56380593776703003</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>0.56532961130142001</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>0.55798184871673995</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>0.55798184871673995</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>0.56239098310471003</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>0.56506597995758001</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>0.55951815843581998</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>0.56195771694183005</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>0.55517184734344005</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>0.55862081050873003</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>0.55753439664840998</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>0.56103628873824996</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>0.56122833490372004</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>0.55507487058640004</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>0.55476605892180997</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>0.55161023139954002</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>0.56206285953521995</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>0.55902951955794999</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>0.56243318319321001</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>0.56486892700195002</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>0.56175011396408003</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>0.55375319719314997</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>0.56295210123062001</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>0.55225229263305997</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>0.56557106971741</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>0.55561637878418002</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>0.56288272142410001</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>0.55662852525711004</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>0.55535763502121005</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>0.54881364107132002</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>0.55942124128341997</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>0.55732166767119995</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>0.55687719583510997</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>0.55613100528716997</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>0.55333638191223</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>0.55855733156204002</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>0.55350172519684004</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>0.54943931102752996</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>0.55109608173369995</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>0.55072480440140004</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>0.55775600671768</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>0.55104809999465998</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>0.54805302619934004</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>0.54895073175429998</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>0.53992539644241</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>0.55092144012451005</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>0.55404102802277</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>0.54964560270309004</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>0.54443383216857999</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>0.54566580057143999</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>0.54992854595184004</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>0.54900389909743996</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>0.55087858438491999</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>0.54852211475372004</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>0.55394047498703003</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>0.54685896635055997</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>0.55443948507309004</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>0.54928910732268998</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>0.53688633441925004</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>0.55184113979339999</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>0.54171556234359997</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>0.55274593830108998</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>0.54977560043335005</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>0.53987479209900002</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>0.54912412166595004</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>0.54034513235091997</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>0.54089009761810003</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>0.53649127483367998</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>0.54151111841202004</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>0.54689699411392001</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>0.53678494691848999</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>0.54248058795928999</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>0.53854244947433005</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>0.54466140270232999</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>0.54221230745315996</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>0.53583991527556996</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>0.53962165117264005</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>0.54128056764603005</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>0.54353725910187001</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>0.54151684045792003</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>0.53524595499038996</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>0.54018068313598999</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>0.54096621274947998</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>0.54397028684616</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>0.53588610887527</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>0.54216891527176003</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>0.54315727949142001</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>0.53789693117142001</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>0.53884601593018</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>0.53779697418213002</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>0.54250401258469005</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>0.53370827436446999</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>0.53925043344498003</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>0.53811997175216997</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>0.53366249799728005</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>0.53213608264922996</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>0.53480327129364003</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>0.53858542442321999</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>0.53764176368713001</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>0.53929841518402</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>0.53462827205658003</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>0.53491240739821999</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>0.53222191333770996</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>0.53440070152283004</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>0.53761929273605003</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>0.52758753299713002</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>0.53131693601607999</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>0.52851760387420998</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>0.52998477220535001</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>0.53447341918945002</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>0.52459663152695002</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>0.53744614124297996</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>0.52826428413391002</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>0.54070997238159002</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>0.52992296218872004</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>0.52931803464890004</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>0.53101807832717995</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>0.52670454978943004</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>0.53189587593079002</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>0.52524089813232</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>0.52703863382339</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>0.52741128206252996</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>0.52267175912857</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>0.53063076734543002</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>0.54131025075911998</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>0.52723968029021995</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>0.52507728338241999</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>0.52413237094878995</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>0.51793903112410999</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>0.52713352441787997</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>0.52486026287079002</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>0.52396374940872004</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>0.52363890409470004</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>0.53021687269211004</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>0.52663141489028997</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>0.52532666921616</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>0.52670210599899003</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>0.51999920606613004</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>0.52231490612029996</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>0.52214330434798994</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>0.52380484342574996</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>0.53026801347732999</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>0.52356815338134999</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>0.52617621421813998</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>0.52233219146729004</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>0.52398443222045998</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>0.52228891849518</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>0.52325624227524004</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>0.51785111427306996</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>0.51912683248519997</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>0.51527452468872004</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>0.51698237657546997</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>0.51792722940445002</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>0.52101451158524004</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>0.51834231615066995</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>0.52220034599303999</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>0.52292221784591997</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>0.50766921043395996</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>0.51723682880402</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>0.51939362287520996</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>0.51801246404648005</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>0.52250444889069003</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>0.51083666086196999</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>0.51459360122680997</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>0.52100622653961004</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>0.51671814918518</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>0.51367044448853005</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>0.51828563213348</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>0.51400244235991999</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>0.51392543315886996</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>0.51219856739044001</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>0.51602834463119995</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>0.51560962200164995</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>0.52258217334747004</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>0.50293493270874001</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>0.51222854852676003</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>0.51376801729202004</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>0.51797628402710005</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>0.51424419879912997</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>0.51047068834304998</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>0.51423203945160001</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>0.51097232103348</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>0.51077347993850997</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>0.50483590364455999</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>0.51714962720871005</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>0.5169233083725</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>0.51186710596085006</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>0.50802874565125</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>0.50580567121506004</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>0.51214343309402</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>0.50515323877335006</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>0.50987106561661</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>0.50976926088332997</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>0.50584661960601995</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>0.50720548629760998</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>0.50657337903975996</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>0.50146669149399004</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>0.50909376144409002</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>0.50768494606018</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>0.50882846117019997</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>0.50708204507828003</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>0.49922224879264998</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>0.51028555631637995</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>0.50266635417937999</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>0.50530523061751997</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>0.50364696979523005</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>0.50421625375748003</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>0.50412166118622004</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>0.49836960434914002</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>0.51170557737349998</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>0.50199294090270996</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>0.50297504663466996</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>0.50714629888535001</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>0.50617843866348</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>0.50539726018905995</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>0.50017809867858998</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>0.50147128105163996</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>0.50011712312697998</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>0.50349754095078003</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>0.49955037236214</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>0.50648653507232999</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>0.49923437833786</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>0.50227618217467995</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>0.49634584784508001</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>0.50252342224121005</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>0.50897532701491999</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>0.50562542676926003</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>0.50760048627853005</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>0.49953627586365001</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>0.50514149665832997</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>0.49617886543273998</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>0.49441823363303999</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>0.50136935710907005</c:v>
+                </c:pt>
+                <c:pt idx="497">
+                  <c:v>0.50123035907744995</c:v>
+                </c:pt>
+                <c:pt idx="498">
+                  <c:v>0.50542825460434004</c:v>
+                </c:pt>
+                <c:pt idx="499">
+                  <c:v>0.49867099523544001</c:v>
+                </c:pt>
+                <c:pt idx="501">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="502">
+                  <c:v>0.50163699388503991</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8E9B-4F7A-92C3-862DA76D7AEE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Worksheet!$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>val_loss</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Worksheet!$F$2:$F$504</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="503"/>
+                <c:pt idx="0">
+                  <c:v>1.2508552074432</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.2449514865875</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.2293705940246999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.2296992540359</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.2128093242644999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.1862288713455</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.1738427877426001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.1692280769348</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.1598997116089</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.1330070495605</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.1255904436110999</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.1415003538132</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.0829355716705</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.0711005926132</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.0274316072464</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.0367410182953001</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.99584239721297996</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.93404966592788996</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.89817196130752996</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.88808691501616999</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.89364856481552002</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.85428655147552002</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.84759265184402</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.86586767435073997</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.87455385923385998</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.85881584882735995</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.81069868803024003</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.79560130834579001</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.78761786222457997</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.77347421646117998</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.72895908355713002</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.71113288402556996</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.70910215377807995</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.69329065084456998</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.69770675897598</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.69497853517532004</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.69961017370223999</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.68876099586487005</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.67142820358276001</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.67330330610275002</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.66384267807007002</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.66989064216614003</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.67322289943695002</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.66475230455399004</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.67734831571579002</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.66546994447707997</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.65514832735062001</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.64865303039551003</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.64767974615097001</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.64867824316025002</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.66555964946747004</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.64319235086440996</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.64465481042862005</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.63124293088912997</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.68254882097243996</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.63682961463928001</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.62023568153381003</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.62173104286194003</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.62031406164169001</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.61359387636185003</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.60037899017333995</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.59847414493561002</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.59860140085220004</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.59689152240752996</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.59499037265777999</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.59311968088150002</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.59408909082412997</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.59349149465561002</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.59268045425414995</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.59142261743545999</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.59105360507964999</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.59775775671005005</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.58988314867019997</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.59462779760360995</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.59103679656982</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.58806908130645996</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.58861994743347001</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.59287965297698997</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.59075188636779996</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.58606916666030995</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>0.58656287193297996</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>0.58758229017258001</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>0.58842873573303001</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>0.58567988872527998</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>0.58884054422378995</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>0.58777695894241</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>0.58469551801681996</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>0.58649921417235995</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>0.58464908599854004</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>0.58026045560837003</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>0.58699667453766002</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>0.58624571561812999</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>0.57834303379059004</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0.58457785844803001</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>0.58563327789306996</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>0.58580183982848999</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0.57925903797150002</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>0.58405816555023005</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>0.58055251836777</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>0.58539330959320002</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>0.59074342250823997</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>0.57660090923309004</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>0.57849025726318004</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>0.5779834985733</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>0.57960736751555997</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>0.58332759141921997</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>0.57561606168747004</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>0.57666617631911998</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>0.58004480600357</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>0.57664859294891002</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>0.58350878953934004</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>0.57465654611588002</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>0.57593637704848999</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>0.57819998264312999</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>0.57361894845963002</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>0.57352370023726995</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>0.57502174377440995</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>0.57261413335800004</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>0.57569921016693004</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>0.58309996128081998</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>0.57218718528748003</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>0.57595354318618996</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>0.57146215438842995</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>0.57110971212386996</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>0.57093018293381004</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>0.56937497854232999</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>0.56890481710434004</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>0.57049834728241</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>0.57479292154312001</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>0.56938576698303001</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>0.57049185037613004</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>0.57169365882874001</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>0.56544804573059004</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>0.56407988071441995</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>0.56903034448624001</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>0.57073462009429998</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>0.56453198194503995</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>0.56884676218033003</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>0.56246012449265004</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>0.56450331211089999</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>0.56431436538696</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>0.56618976593018</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>0.57049781084061002</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>0.56419086456298995</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>0.56441384553909002</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>0.56663078069687001</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>0.57100492715836004</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>0.56187534332275002</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>0.56931132078170998</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>0.56768703460693004</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>0.56507539749145996</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>0.56332278251648005</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>0.56145900487900002</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>0.56788969039917003</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>0.57128751277923995</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>0.56228905916214</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>0.56986528635025002</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>0.55877208709716997</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>0.55431300401688</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>0.56455725431442005</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>0.56078672409057995</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>0.56522655487061002</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>0.57032018899918002</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>0.55916333198546997</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>0.55425697565079002</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>0.55808758735657005</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>0.56927567720412997</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>0.55743300914764005</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>0.56401330232619995</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>0.56244981288910001</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>0.56387937068938998</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>0.55613780021667003</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>0.56139159202575994</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>0.56889861822127996</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>0.55827772617339999</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>0.57080948352813998</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>0.56831002235412997</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>0.55627459287643</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>0.56739765405654996</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>0.55277436971663996</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>0.56509274244308005</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>0.55423450469971003</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>0.55005329847336004</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>0.55423992872238004</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>0.55509787797928001</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>0.55869168043136996</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>0.56108850240706998</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>0.55426973104476995</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>0.56031322479248002</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>0.54812163114547996</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>0.55680865049362005</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>0.56622415781020996</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>0.56040918827056996</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>0.55867999792098999</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>0.55867677927017001</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>0.56038957834243996</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>0.55090320110321001</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>0.56107389926910001</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>0.55136549472809004</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>0.55216604471206998</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>0.54917204380035001</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>0.54484272003173995</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>0.56532555818557995</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>0.54973018169402998</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>0.55396020412445002</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>0.54971462488174005</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>0.56909346580505005</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>0.54280722141266002</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>0.54318386316299005</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>0.54660493135452004</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>0.54689687490463001</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>0.54084032773972002</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>0.54778605699538996</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>0.54225516319275002</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>0.54802709817885997</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>0.54469394683838002</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>0.54013842344284002</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>0.54039943218231001</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>0.54258096218108998</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>0.54492419958115001</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>0.54463994503020996</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>0.54917758703232</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>0.54000031948089999</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>0.55830264091491999</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>0.53913360834122004</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>0.54090440273285001</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>0.54012709856033003</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>0.53972429037094005</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>0.53930467367171997</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>0.54427593946456998</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>0.54570943117142001</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>0.53263670206070002</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>0.53281742334366</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>0.53337848186492998</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>0.53844398260116999</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>0.53832262754439997</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>0.54424571990966997</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>0.53884851932526001</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>0.54828244447707997</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>0.54453521966934004</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>0.53338450193404996</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>0.54643827676773005</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>0.53497499227524004</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>0.53281033039092995</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>0.53410881757735995</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>0.53455489873885997</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>0.54105883836746005</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>0.53880769014358998</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>0.52932858467101995</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>0.53768521547318004</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>0.53291279077529996</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>0.53076344728470004</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>0.54083055257796997</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>0.53095680475234996</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>0.53911846876143998</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>0.53119450807571</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>0.53632408380508001</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>0.52831834554671997</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>0.54060822725295998</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>0.53823113441466996</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>0.53265368938446001</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>0.52065414190292003</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>0.53110188245773005</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>0.53477108478545998</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>0.52425616979598999</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>0.53118199110030995</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>0.52329111099242998</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>0.53043925762177002</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>0.5376198887825</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>0.52899044752121005</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>0.52816838026046997</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>0.53380095958710005</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>0.53338348865509</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>0.53732520341873002</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>0.52307325601578003</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>0.53073978424071999</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>0.52768474817276001</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>0.51767867803573997</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>0.52454966306686002</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>0.54626888036728005</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>0.52356171607971003</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>0.51916092634201005</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>0.54756677150725996</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>0.52686834335327004</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>0.52495151758194003</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>0.52486950159072998</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>0.51705288887024003</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>0.53344333171844005</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>0.53534561395644997</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>0.51909059286117998</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>0.52231639623642001</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>0.52747529745101995</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>0.52841645479202004</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>0.51780813932419001</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>0.52299994230269997</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>0.51831185817719005</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>0.51475304365158003</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>0.53114342689514005</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>0.51574802398681996</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>0.52156031131743996</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>0.51582175493240001</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>0.52692109346390004</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>0.51537472009659002</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>0.51398390531539995</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>0.52175927162169999</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>0.53049528598785001</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>0.53261309862136996</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>0.52834182977676003</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>0.52203661203384</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>0.52489757537841997</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>0.52066898345946999</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>0.52173286676407005</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>0.52150422334670998</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>0.53727287054062001</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>0.53673356771469005</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>0.51539927721024004</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>0.51670479774474998</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>0.53368318080902</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>0.52484589815140004</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>0.54635083675384999</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>0.52331221103668002</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>0.52408337593079002</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>0.51935631036758001</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>0.51320743560791005</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>0.50930726528168002</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>0.51787525415420999</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>0.51320183277130005</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>0.51233822107314997</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>0.52926498651505005</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>0.53109884262085005</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>0.51564496755599998</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>0.51584720611571999</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>0.51259851455687999</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>0.53172641992569003</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>0.52593308687210005</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>0.56525182723999001</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>0.55359429121017001</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>0.52123570442199996</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>0.52037262916564997</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>0.50895661115645996</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>0.51723819971085006</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>0.53787988424301003</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>0.50590485334395996</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>0.51769500970839999</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>0.51431643962859996</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>0.51598644256591997</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>0.54176962375641002</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>0.50613176822661998</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>0.50532621145248002</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>0.52917230129241999</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>0.50908696651458996</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>0.51869583129883001</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>0.50992184877395996</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>0.51854085922241</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>0.55121517181395996</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>0.51762491464615001</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>0.50629901885985995</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>0.52141004800796997</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>0.50477099418640003</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>0.51605480909348</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>0.50475329160689997</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>0.51257884502411</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>0.5125538110733</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>0.50652045011519997</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>0.50692427158356002</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>0.49798604846000999</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>0.50538736581802002</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>0.50561219453812001</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>0.51655745506286999</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>0.50440174341202004</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>0.50747847557068004</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>0.50864452123642001</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>0.50887483358383001</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>0.50438225269318004</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>0.51362371444702004</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>0.51253747940062999</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>0.50634944438934004</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>0.53392124176025002</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>0.50169688463211004</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>0.51202994585036998</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>0.53398853540420999</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>0.51121044158936002</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>0.49683749675750999</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>0.50221866369247004</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>0.49332365393638999</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>0.50181031227112005</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>0.50773590803145996</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>0.51722717285155995</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>0.50168049335480003</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>0.49662315845490002</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>0.50189208984375</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>0.50880956649779996</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>0.50044023990631004</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>0.49863597750664002</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>0.51463168859482</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>0.49602171778679</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>0.52457183599472001</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>0.49759677052498003</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>0.50985932350159002</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>0.49976092576981002</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>0.49586987495422002</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>0.51009470224380005</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>0.50235348939895996</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>0.51398158073425004</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>0.4973019361496</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>0.48925271630286998</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>0.49873623251915</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>0.49682173132896001</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>0.49469447135924999</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>0.49057498574257002</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>0.50608193874358998</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>0.51179301738739003</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>0.51177829504012995</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>0.51186156272887995</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>0.48835811018943998</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>0.49076887965201998</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>0.48873054981232</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>0.48996081948280001</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>0.4945524930954</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>0.48652738332748002</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>0.48990401625633001</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>0.50724297761917003</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>0.49327805638312999</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>0.49116006493567999</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>0.4942861199379</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>0.48587968945503002</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>0.48719480633736001</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>0.48813486099242998</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>0.50806182622910001</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>0.48964419960976002</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>0.4899874329567</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>0.49807509779929998</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>0.48424473404884</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>0.48920747637749001</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>0.48892295360565002</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>0.48343405127525002</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>0.48688533902168002</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>0.49234887957572998</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>0.48776054382324002</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>0.48280191421509</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>0.48461803793906999</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>0.48520213365554998</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>0.48811924457549999</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>0.48388481140137002</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>0.48419210314750999</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>0.48475027084351002</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>0.4825287759304</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>0.48420715332031</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>0.51173776388168002</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>0.48198273777961997</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>0.48385602235794001</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>0.49508720636367998</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>0.49696043133736001</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>0.48950213193893</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>0.50144016742705999</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>0.49209156632423001</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>0.47976785898209001</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>0.49731779098510998</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>0.49014264345169001</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>0.4831183552742</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>0.48459795117378002</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>0.49083366990089</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>0.49130228161812001</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>0.48245784640312001</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>0.48932066559791998</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>0.50442111492157005</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>0.48152324557303999</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>0.48053634166718001</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>0.47778427600861001</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>0.48906233906745999</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>0.47600367665290999</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>0.47987800836562999</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>0.47886559367179998</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>0.47790616750717002</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>0.47778692841530002</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>0.47317785024643</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>0.48934707045554998</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>0.47839000821114003</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>0.51032090187072998</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>0.48735520243644997</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>0.48054632544518</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>0.48303520679473999</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>0.49292811751366</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>0.48007783293723999</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>0.48118746280669999</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>0.47745129466057001</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>0.48011353611946</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>0.47990527749062001</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>0.48070126771927002</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>0.47456744313240001</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>0.48374891281128002</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>0.48251459002495001</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>0.48808625340461997</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>0.47206476330757002</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>0.48245602846146002</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>0.51462632417679</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>0.48662722110748002</c:v>
+                </c:pt>
+                <c:pt idx="497">
+                  <c:v>0.48785230517387002</c:v>
+                </c:pt>
+                <c:pt idx="498">
+                  <c:v>0.47044152021407998</c:v>
+                </c:pt>
+                <c:pt idx="499">
+                  <c:v>0.47114208340644997</c:v>
+                </c:pt>
+                <c:pt idx="501">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="502">
+                  <c:v>0.4821532547473914</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-8E9B-4F7A-92C3-862DA76D7AEE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="603335664"/>
+        <c:axId val="609308064"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="603335664"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="499"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="pt-BR" sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Epochs</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="609308064"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="609308064"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="pt-BR" sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Loss</a:t>
+                </a:r>
+                <a:endParaRPr lang="pt-BR" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:sysClr>
+                  </a:solidFill>
+                </a:endParaRPr>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="603335664"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -7104,6 +14182,1038 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -7140,6 +15250,608 @@
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>402</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>7043</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>186142</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Gráfico 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0919A412-09C3-4B4E-B2B3-8456F29E9D1C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>608360</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>7043</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Gráfico 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F763DF1-EA21-4054-8FAB-FB1F8907DA88}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>270012</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>145774</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>271668</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>39756</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="Retângulo: Cantos Arredondados 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E039B5CD-6C09-40F2-9905-6FCCA1C960AA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13083208" y="12337774"/>
+          <a:ext cx="1227482" cy="655982"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1600" b="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Validation Loss</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>289892</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>107673</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>321365</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>56319</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="Retângulo: Cantos Arredondados 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2331FF5D-B0C4-4D3D-9117-B6B3DAC74704}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16167653" y="10394673"/>
+          <a:ext cx="1257299" cy="710646"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1600" b="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Training Loss </a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>571501</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>107674</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>346214</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>72886</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="7" name="Conector de Seta Reta 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F3413DAB-4FC2-4DC2-B084-0ADCE7D421F5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="7255566" y="10394674"/>
+          <a:ext cx="387626" cy="536712"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>240196</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>132522</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>16565</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>182218</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="9" name="Conector de Seta Reta 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E2F4918-5478-471D-AEF0-3D1561649817}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="14279218" y="11943522"/>
+          <a:ext cx="389282" cy="430696"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>414130</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>14909</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>331304</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>115957</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="10" name="Conector de Seta Reta 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FA7ED6CB-5068-4BC7-9781-2DED4FAF4646}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="15678978" y="11063909"/>
+          <a:ext cx="530087" cy="672548"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>115956</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>16565</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>117613</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>101047</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="Retângulo: Cantos Arredondados 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E57CC609-0E38-42A5-94DE-E445C7511644}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9251673" y="10875065"/>
+          <a:ext cx="1227483" cy="655982"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1600" b="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Validation Accuracy</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>293202</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>53008</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>294858</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>137490</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="Retângulo: Cantos Arredondados 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{22C9B2E6-34C0-4F90-BBCE-3694FB9CFD96}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7590180" y="10911508"/>
+          <a:ext cx="1227482" cy="655982"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1600" b="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Training Accuracy</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>2</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>157371</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>49697</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="25" name="Conector: Curvo 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{116AD5A5-D3BE-F4DD-BDDE-2D8B94E76BA4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000" flipH="1">
+          <a:off x="8406849" y="10021958"/>
+          <a:ext cx="1002195" cy="770283"/>
+        </a:xfrm>
+        <a:prstGeom prst="curvedConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 150000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
